--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6352,222 +6352,222 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>CMWG2527</t>
+          <t>CMWG2603</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>5,600</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>CMWG2603</t>
+          <t>CMWG2604</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>5,600</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>19,000,000</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>88,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>CMWG2604</t>
+          <t>CMWG2609</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>4,400</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>19,000,000</t>
+          <t>13,000,000</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>CMWG2609</t>
+          <t>CMWG2610</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>4,400</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>13,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>CMWG2610</t>
+          <t>CMWG2611</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>101,000</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>CMWG2611</t>
+          <t>CMWG2612</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -6577,118 +6577,118 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>101,000</t>
+          <t>84,200</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>CMWG2612</t>
+          <t>CMWG2616</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>84,200</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>CMWG2616</t>
+          <t>CMWG2617</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>75,500</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>CMWG2617</t>
+          <t>CMWG2618</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -6698,17 +6698,17 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -6718,61 +6718,61 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>75,500</t>
+          <t>77,000</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>CMWG2618</t>
+          <t>CMWG2619</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>77,000</t>
+          <t>72,200</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>28/12/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>CMWG2619</t>
+          <t>CMWG2620</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -6802,29 +6802,29 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>72,200</t>
+          <t>74,000</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>CMWG2620</t>
+          <t>CMWG2621</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6834,71 +6834,71 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>3,200</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>74,000</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>CMWG2621</t>
+          <t>CMWG2622</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>9.85 : 1</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>88,000</t>
+          <t>73,456</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>CMWG2622</t>
+          <t>CMWG2623</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -6918,17 +6918,17 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>73,456</t>
+          <t>82,712</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -6940,49 +6940,49 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>CMWG2623</t>
+          <t>CMWG2624</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>9.85 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>21,500,000</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>82,712</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>CMWG2624</t>
+          <t>CMWG2625</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -7002,81 +7002,81 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>21,500,000</t>
+          <t>24,000,000</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>CMWG2625</t>
+          <t>CSHB2606</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>24,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>CSHB2606</t>
+          <t>CSHB2607</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>15,500</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>CSHB2607</t>
+          <t>CSHB2608</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -7138,24 +7138,24 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>15,500</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>CSHB2608</t>
+          <t>CSHB2609</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -7165,34 +7165,34 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>16,333</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>CSHB2609</t>
+          <t>CSHB2610</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7222,19 +7222,19 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>16,333</t>
+          <t>15,999</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>CSHB2610</t>
+          <t>CSHB2611</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -7264,19 +7264,19 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>15,999</t>
+          <t>14,999</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>CSHB2611</t>
+          <t>CSHB2612</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -7306,29 +7306,29 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>14,999</t>
+          <t>16,789</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>CSHB2612</t>
+          <t>CSHB2613</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -7343,24 +7343,24 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>16,789</t>
+          <t>13,100</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/12/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>CSHB2613</t>
+          <t>CSHB2614</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -7390,66 +7390,66 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>13,100</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>CSHB2614</t>
+          <t>CSHB2615</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>CSHB2615</t>
+          <t>CSHB2616</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>CSHB2616</t>
+          <t>CSHB2617</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -7516,24 +7516,24 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>15,500</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>CSHB2617</t>
+          <t>CSHB2618</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -7548,29 +7548,29 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>15,500</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>CSHB2618</t>
+          <t>CSHB2619</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7590,39 +7590,39 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>CSHB2619</t>
+          <t>CSHB2620</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7632,91 +7632,91 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>12,500</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>CSHB2620</t>
+          <t>CSSB2603</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>06/05/2027</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>CSSB2603</t>
+          <t>CSSB2604</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -7726,19 +7726,19 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>17,777</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>06/05/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>CSSB2604</t>
+          <t>CSSB2605</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -7768,19 +7768,19 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>17,777</t>
+          <t>17,111</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>CSSB2605</t>
+          <t>CSSB2606</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7810,19 +7810,19 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>17,111</t>
+          <t>15,999</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>CSSB2606</t>
+          <t>CSSB2607</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7852,103 +7852,103 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>15,999</t>
+          <t>16,888</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>CSSB2607</t>
+          <t>CSTB2533</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>17 tháng</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>16,888</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>CSTB2533</t>
+          <t>CSTB2536</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>17 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>CSTB2536</t>
+          <t>CSTB2537</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -7978,113 +7978,113 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>CSTB2537</t>
+          <t>CSTB2603</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>CSTB2603</t>
+          <t>CSTB2604</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>19,000,000</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>CSTB2604</t>
+          <t>CSTB2606</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -8094,128 +8094,128 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>19,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>CSTB2606</t>
+          <t>CSTB2608</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>CSTB2608</t>
+          <t>CSTB2609</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>CSTB2609</t>
+          <t>CSTB2610</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -8225,24 +8225,24 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>74,700</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>CSTB2610</t>
+          <t>CSTB2611</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -8272,61 +8272,61 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>74,700</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>CSTB2611</t>
+          <t>CSTB2612</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>80,888</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>CSTB2612</t>
+          <t>CSTB2613</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -8356,19 +8356,19 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>80,888</t>
+          <t>77,777</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>CSTB2613</t>
+          <t>CSTB2614</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>77,777</t>
+          <t>78,888</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>CSTB2614</t>
+          <t>CSTB2615</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -8420,17 +8420,17 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -8440,103 +8440,103 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>78,888</t>
+          <t>81,888</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>CSTB2615</t>
+          <t>CSTB2619</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>81,888</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>CSTB2619</t>
+          <t>CSTB2620</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>CSTB2620</t>
+          <t>CSTB2621</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -8546,17 +8546,17 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -8566,39 +8566,39 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>71,500</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>CSTB2621</t>
+          <t>CSTB2622</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>3,100</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -8608,19 +8608,19 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>71,500</t>
+          <t>69,700</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>28/12/2026</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>CSTB2622</t>
+          <t>CSTB2623</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>3,100</t>
+          <t>3,300</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -8650,66 +8650,66 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>69,700</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>CSTB2623</t>
+          <t>CSTB2624</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>3,300</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>81,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>CSTB2624</t>
+          <t>CSTB2625</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -8719,17 +8719,17 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -8746,49 +8746,49 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CSTB2625</t>
+          <t>CSTB2626</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>3,700</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>71,500</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>CSTB2626</t>
+          <t>CSTB2627</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -8808,17 +8808,17 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>71,500</t>
+          <t>81,100</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -8830,49 +8830,49 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CSTB2627</t>
+          <t>CSTB2628</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>24,000,000</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>81,100</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>CSTB2628</t>
+          <t>CSTB2629</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -8892,113 +8892,113 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>1,668</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>24,000,000</t>
+          <t>21,500,000</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>CSTB2629</t>
+          <t>CTCB2521</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>17 tháng</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>1,668</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>21,500,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>42,600</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>CTCB2521</t>
+          <t>CTCB2522</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>17 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>42,600</t>
+          <t>44,500</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>CTCB2522</t>
+          <t>CTCB2523</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -9028,29 +9028,29 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>44,500</t>
+          <t>45,500</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>CTCB2523</t>
+          <t>CTCB2601</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -9060,76 +9060,76 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>19,000,000</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>45,500</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>22/10/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>CTCB2601</t>
+          <t>CTCB2603</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VPBank ( VPX )</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>19,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>CTCB2603</t>
+          <t>CTCB2605</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VPBank ( VPX )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9139,202 +9139,202 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>4,700</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>CTCB2605</t>
+          <t>CTCB2606</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>4,700</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>39,500</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>CTCB2606</t>
+          <t>CTCB2607</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3.92 : 1</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>39,500</t>
+          <t>35,259</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>CTCB2607</t>
+          <t>CTCB2611</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>3.92 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>35,259</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>CTCB2611</t>
+          <t>CTCB2612</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>CTCB2612</t>
+          <t>CTCB2613</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -9344,17 +9344,17 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -9364,39 +9364,39 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>30,500</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>CTCB2613</t>
+          <t>CTCB2614</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
@@ -9406,103 +9406,103 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>30,500</t>
+          <t>35,500</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>CTCB2614</t>
+          <t>CTCB2615</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>35,500</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>CTCB2615</t>
+          <t>CTCB2616</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>31,700</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>CTCB2616</t>
+          <t>CTCB2617</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -9522,17 +9522,17 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>31,700</t>
+          <t>35,700</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -9544,49 +9544,49 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>CTCB2617</t>
+          <t>CTCB2618</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>35,700</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CTCB2618</t>
+          <t>CTCB2619</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9606,59 +9606,59 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>CTCB2619</t>
+          <t>CTPB2605</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -9670,22 +9670,22 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CTPB2605</t>
+          <t>CTPB2606</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -9705,56 +9705,56 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>06/05/2027</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>CTPB2606</t>
+          <t>CTPB2607</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>19,399</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>06/05/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>CTPB2607</t>
+          <t>CTPB2608</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9774,34 +9774,34 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>19,399</t>
+          <t>18,888</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>CTPB2608</t>
+          <t>CTPB2609</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -9811,39 +9811,39 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>18,888</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>CTPB2609</t>
+          <t>CTPB2610</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -9880,49 +9880,49 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>CTPB2610</t>
+          <t>CTPB2611</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>CTPB2611</t>
+          <t>CTPB2612</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -9942,17 +9942,17 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>CTPB2612</t>
+          <t>CVHM2523</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -9979,34 +9979,34 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CVHM2523</t>
+          <t>CVHM2524</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -10036,29 +10036,29 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>147,000</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>CVHM2524</t>
+          <t>CVHM2603</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -10068,34 +10068,34 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>4,800</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>147,000</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CVHM2603</t>
+          <t>CVHM2604</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10105,160 +10105,160 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>106,000</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>CVHM2604</t>
+          <t>CVHM2607</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>106,000</t>
+          <t>135,000</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CVHM2607</t>
+          <t>CVHM2609</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>9 : 1</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>135,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>CVHM2609</t>
+          <t>CVHM2610</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>9 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>186,000</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CVHM2610</t>
+          <t>CVHM2611</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -10288,61 +10288,61 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>190,000</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>CVHM2611</t>
+          <t>CVHM2612</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>190,000</t>
+          <t>169,999</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CVHM2612</t>
+          <t>CVHM2613</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10367,24 +10367,24 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>169,999</t>
+          <t>173,979</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>CVHM2613</t>
+          <t>CVHM2614</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -10409,108 +10409,108 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>173,979</t>
+          <t>176,868</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CVHM2614</t>
+          <t>CVHM2615</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>176,868</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>CVHM2615</t>
+          <t>CVHM2616</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>9.63 : 1</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>75,641</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CVHM2616</t>
+          <t>CVHM2617</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -10530,17 +10530,17 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>75,641</t>
+          <t>85,800</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -10552,49 +10552,49 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>CVHM2617</t>
+          <t>CVHM2618</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>9.63 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>85,800</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CVHM2618</t>
+          <t>CVHM2619</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10614,39 +10614,39 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>1,868</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>CVHM2619</t>
+          <t>CVHM2620</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10656,81 +10656,81 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>1,868</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>76,000</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CVHM2620</t>
+          <t>CVIB2513</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>CVIB2513</t>
+          <t>CVIB2601</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10740,76 +10740,76 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CVIB2601</t>
+          <t>CVIB2604</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1.90 : 1</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>17,540</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>CVIB2604</t>
+          <t>CVIB2605</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>1.90 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -10829,34 +10829,34 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>17,540</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CVIB2605</t>
+          <t>CVIB2606</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10866,71 +10866,71 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>17,500</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>CVIB2606</t>
+          <t>CVIB2607</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>17,500</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CVIB2607</t>
+          <t>CVIB2608</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -10950,17 +10950,17 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -10972,49 +10972,49 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>CVIB2608</t>
+          <t>CVIB2609</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>15,527</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CVIB2609</t>
+          <t>CVIB2610</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -11034,39 +11034,39 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>15,527</t>
+          <t>14,613</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>CVIB2610</t>
+          <t>CVIB2611</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -11076,71 +11076,71 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>14,613</t>
+          <t>13,700</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CVIB2611</t>
+          <t>CVIC2515</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>13,700</t>
+          <t>245,000</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>CVIC2515</t>
+          <t>CVIC2516</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -11170,39 +11170,39 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>245,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CVIC2516</t>
+          <t>CVIC2602</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -11212,19 +11212,19 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>248,888</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>CVIC2602</t>
+          <t>CVIC2603</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11244,29 +11244,29 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>248,888</t>
+          <t>250,789</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CVIC2603</t>
+          <t>CVIC2604</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -11296,19 +11296,19 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>250,789</t>
+          <t>252,789</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/01/2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>CVIC2604</t>
+          <t>CVIC2605</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -11328,29 +11328,29 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>252,789</t>
+          <t>244,567</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>26/01/2027</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CVIC2605</t>
+          <t>CVIC2606</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -11375,108 +11375,108 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>244,567</t>
+          <t>246,789</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>CVIC2606</t>
+          <t>CVIC2607</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,700</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>246,789</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CVIC2607</t>
+          <t>CVIC2608</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>221,200</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>CVIC2608</t>
+          <t>CVIC2609</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -11496,17 +11496,17 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>221,200</t>
+          <t>244,000</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -11518,49 +11518,49 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CVIC2609</t>
+          <t>CVIC2610</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>CVIC2610</t>
+          <t>CVIC2611</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11585,66 +11585,66 @@
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CVIC2611</t>
+          <t>CVJC2602</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>152,252</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>CVJC2602</t>
+          <t>CVJC2603</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -11669,24 +11669,24 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>152,252</t>
+          <t>158,205</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CVJC2603</t>
+          <t>CVJC2604</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -11711,66 +11711,66 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>158,205</t>
+          <t>154,606</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>CVJC2604</t>
+          <t>CVJC2605</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>154,606</t>
+          <t>132,500</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CVJC2605</t>
+          <t>CVJC2606</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -11790,17 +11790,17 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>132,500</t>
+          <t>153,500</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -11812,96 +11812,96 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>CVJC2606</t>
+          <t>CVNM2523</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>9.56 : 1</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>153,500</t>
+          <t>60,322</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CVNM2523</t>
+          <t>CVNM2601</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>9.56 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>60,322</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>CVNM2601</t>
+          <t>CVNM2603</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11911,17 +11911,17 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -11931,118 +11931,118 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CVNM2603</t>
+          <t>CVNM2605</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>CVNM2605</t>
+          <t>CVNM2606</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CVNM2606</t>
+          <t>CVNM2607</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -12052,29 +12052,29 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>CVNM2607</t>
+          <t>CVNM2608</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -12084,29 +12084,29 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>66,999</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CVNM2608</t>
+          <t>CVNM2609</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -12136,24 +12136,24 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>66,999</t>
+          <t>70,111</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>CVNM2609</t>
+          <t>CVNM2613</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -12163,34 +12163,34 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>2.91 : 1</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>70,111</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CVNM2613</t>
+          <t>CVNM2614</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -12200,17 +12200,17 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>2.91 : 1</t>
+          <t>3.88 : 1</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
@@ -12225,103 +12225,103 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>CVNM2614</t>
+          <t>CVNM2615</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>3.88 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>54,500</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CVNM2615</t>
+          <t>CVNM2616</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>54,500</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>CVNM2616</t>
+          <t>CVNM2617</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12331,34 +12331,34 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>58,000</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CVNM2617</t>
+          <t>CVNM2618</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12378,155 +12378,155 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>58,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>CVNM2618</t>
+          <t>CVNM2619</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CVNM2619</t>
+          <t>CVPB2528</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>37,300</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>CVPB2528</t>
+          <t>CVPB2531</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>37,300</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CVPB2531</t>
+          <t>CVPB2532</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
@@ -12556,39 +12556,39 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>CVPB2532</t>
+          <t>CVPB2603</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
@@ -12598,29 +12598,29 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CVPB2603</t>
+          <t>CVPB2606</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -12630,39 +12630,39 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>CVPB2606</t>
+          <t>CVPB2608</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -12672,12 +12672,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -12687,66 +12687,66 @@
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CVPB2608</t>
+          <t>CVPB2609</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3.93 : 1</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>29,476</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>CVPB2609</t>
+          <t>CVPB2610</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12761,108 +12761,108 @@
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>29,476</t>
+          <t>28,494</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CVPB2610</t>
+          <t>CVPB2611</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>3.93 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>28,494</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>CVPB2611</t>
+          <t>CVPB2612</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>31,999</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CVPB2612</t>
+          <t>CVPB2613</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -12892,19 +12892,19 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>31,999</t>
+          <t>32,888</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>CVPB2613</t>
+          <t>CVPB2614</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -12924,81 +12924,81 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>32,888</t>
+          <t>33,456</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CVPB2614</t>
+          <t>CVPB2615</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>33,456</t>
+          <t>28,500</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>CVPB2615</t>
+          <t>CVPB2616</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -13008,29 +13008,29 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>28,500</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CVPB2616</t>
+          <t>CVPB2617</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -13040,17 +13040,17 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -13060,108 +13060,108 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>25,500</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>CVPB2617</t>
+          <t>CVPB2618</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>25,500</t>
+          <t>27,200</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CVPB2618</t>
+          <t>CVPB2619</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>27,200</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>CVPB2619</t>
+          <t>CVPB2620</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -13171,22 +13171,22 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -13198,7 +13198,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CVPB2620</t>
+          <t>CVPB2621</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
@@ -13233,24 +13233,24 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>CVPB2621</t>
+          <t>CVPB2622</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -13260,29 +13260,29 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>25,400</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CVPB2622</t>
+          <t>CVPB2623</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -13302,17 +13302,17 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>25,400</t>
+          <t>28,600</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -13324,49 +13324,49 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>CVPB2623</t>
+          <t>CVPB2624</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>28,600</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CVPB2624</t>
+          <t>CVPB2625</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -13386,71 +13386,71 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>CVPB2625</t>
+          <t>CVRE2525</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CVRE2525</t>
+          <t>CVRE2526</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
@@ -13480,103 +13480,103 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>CVRE2526</t>
+          <t>CVRE2603</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CVRE2603</t>
+          <t>CVRE2604</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>35,999</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>CVRE2604</t>
+          <t>CVRE2605</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
@@ -13606,39 +13606,39 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>35,999</t>
+          <t>37,456</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CVRE2605</t>
+          <t>CVRE2606</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
@@ -13648,19 +13648,19 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>37,456</t>
+          <t>28,103</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>CVRE2606</t>
+          <t>CVRE2607</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -13680,17 +13680,17 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>28,103</t>
+          <t>31,870</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -13702,49 +13702,49 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CVRE2607</t>
+          <t>CVRE2608</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>31,870</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>CVRE2608</t>
+          <t>CVRE2609</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -13754,114 +13754,72 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CVRE2609</t>
+          <t>CVRE2610</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
-        <is>
-          <t>11/02/2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>CVRE2610</t>
-        </is>
-      </c>
-      <c r="B319" s="2" t="inlineStr">
-        <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
-        </is>
-      </c>
-      <c r="C319" s="2" t="inlineStr">
-        <is>
-          <t>8 tháng</t>
-        </is>
-      </c>
-      <c r="D319" s="2" t="inlineStr">
-        <is>
-          <t>3 : 1</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="F319" s="2" t="inlineStr">
-        <is>
-          <t>4,000,000</t>
-        </is>
-      </c>
-      <c r="G319" s="2" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="H319" s="2" t="inlineStr">
         <is>
           <t>22/04/2027</t>
         </is>

--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8662,49 +8662,49 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>CSTB2627</t>
+          <t>CSTB2628</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>24,000,000</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>81,100</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>CSTB2628</t>
+          <t>CSTB2629</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -8724,113 +8724,113 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>1,668</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>24,000,000</t>
+          <t>21,500,000</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CSTB2629</t>
+          <t>CTCB2521</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>17 tháng</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>1,668</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>21,500,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>42,600</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>CTCB2521</t>
+          <t>CTCB2522</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>17 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>42,600</t>
+          <t>44,500</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CTCB2522</t>
+          <t>CTCB2523</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -8860,29 +8860,29 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>44,500</t>
+          <t>45,500</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>CTCB2523</t>
+          <t>CTCB2601</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -8892,76 +8892,76 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>19,000,000</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>45,500</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>22/10/2026</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>CTCB2601</t>
+          <t>CTCB2603</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VPBank ( VPX )</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>19,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>CTCB2603</t>
+          <t>CTCB2605</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VPBank ( VPX )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -8971,202 +8971,202 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>4,700</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>CTCB2605</t>
+          <t>CTCB2606</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>4,700</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>39,500</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>CTCB2606</t>
+          <t>CTCB2607</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3.92 : 1</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>39,500</t>
+          <t>35,259</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>CTCB2607</t>
+          <t>CTCB2611</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>3.92 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>35,259</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>CTCB2611</t>
+          <t>CTCB2612</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>CTCB2612</t>
+          <t>CTCB2613</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -9176,17 +9176,17 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -9196,39 +9196,39 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>30,500</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>CTCB2613</t>
+          <t>CTCB2614</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -9238,103 +9238,103 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>30,500</t>
+          <t>35,500</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>CTCB2614</t>
+          <t>CTCB2615</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>35,500</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>CTCB2615</t>
+          <t>CTCB2616</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>31,700</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>CTCB2616</t>
+          <t>CTCB2617</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -9354,17 +9354,17 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>31,700</t>
+          <t>35,700</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -9376,49 +9376,49 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>CTCB2617</t>
+          <t>CTCB2618</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>35,700</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>CTCB2618</t>
+          <t>CTCB2619</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9438,59 +9438,59 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>CTCB2619</t>
+          <t>CTPB2605</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -9502,22 +9502,22 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>CTPB2605</t>
+          <t>CTPB2606</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -9537,56 +9537,56 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>06/05/2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>CTPB2606</t>
+          <t>CTPB2607</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>19,399</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>06/05/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CTPB2607</t>
+          <t>CTPB2608</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9606,34 +9606,34 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>19,399</t>
+          <t>18,888</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>CTPB2608</t>
+          <t>CTPB2609</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9643,39 +9643,39 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>18,888</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CTPB2609</t>
+          <t>CTPB2610</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -9712,49 +9712,49 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>CTPB2610</t>
+          <t>CTPB2611</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>CTPB2611</t>
+          <t>CTPB2612</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -9774,17 +9774,17 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>CTPB2612</t>
+          <t>CVHM2523</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -9811,34 +9811,34 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>CVHM2523</t>
+          <t>CVHM2524</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9868,29 +9868,29 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>147,000</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>CVHM2524</t>
+          <t>CVHM2603</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9900,34 +9900,34 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>4,800</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>147,000</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>CVHM2603</t>
+          <t>CVHM2604</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -9937,160 +9937,160 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>106,000</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>CVHM2604</t>
+          <t>CVHM2607</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>106,000</t>
+          <t>135,000</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CVHM2607</t>
+          <t>CVHM2609</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>9 : 1</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>135,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>CVHM2609</t>
+          <t>CVHM2610</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>9 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>186,000</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CVHM2610</t>
+          <t>CVHM2611</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -10120,61 +10120,61 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>190,000</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>CVHM2611</t>
+          <t>CVHM2612</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>190,000</t>
+          <t>169,999</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CVHM2612</t>
+          <t>CVHM2613</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -10199,24 +10199,24 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>169,999</t>
+          <t>173,979</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>CVHM2613</t>
+          <t>CVHM2614</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -10241,108 +10241,108 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>173,979</t>
+          <t>176,868</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CVHM2614</t>
+          <t>CVHM2615</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>176,868</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>CVHM2615</t>
+          <t>CVHM2616</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>9.63 : 1</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>75,641</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CVHM2616</t>
+          <t>CVHM2617</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -10362,17 +10362,17 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>75,641</t>
+          <t>85,800</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -10384,49 +10384,49 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>CVHM2617</t>
+          <t>CVHM2618</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>9.63 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>85,800</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CVHM2618</t>
+          <t>CVHM2619</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10446,39 +10446,39 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>1,868</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>CVHM2619</t>
+          <t>CVHM2620</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10488,81 +10488,81 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>1,868</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>76,000</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CVHM2620</t>
+          <t>CVIB2513</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>CVIB2513</t>
+          <t>CVIB2601</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10572,76 +10572,76 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CVIB2601</t>
+          <t>CVIB2604</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1.90 : 1</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>17,540</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>CVIB2604</t>
+          <t>CVIB2605</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>1.90 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -10661,34 +10661,34 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>17,540</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CVIB2605</t>
+          <t>CVIB2606</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10698,71 +10698,71 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>17,500</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>CVIB2606</t>
+          <t>CVIB2607</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>17,500</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CVIB2607</t>
+          <t>CVIB2608</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -10782,17 +10782,17 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -10804,49 +10804,49 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>CVIB2608</t>
+          <t>CVIB2609</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>15,527</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CVIB2609</t>
+          <t>CVIB2610</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10866,39 +10866,39 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>15,527</t>
+          <t>14,613</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>CVIB2610</t>
+          <t>CVIB2611</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10908,71 +10908,71 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>14,613</t>
+          <t>13,700</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CVIB2611</t>
+          <t>CVIC2515</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>13,700</t>
+          <t>245,000</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>CVIC2515</t>
+          <t>CVIC2516</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -11002,39 +11002,39 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>245,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CVIC2516</t>
+          <t>CVIC2602</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -11044,19 +11044,19 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>248,888</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>CVIC2602</t>
+          <t>CVIC2603</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -11076,29 +11076,29 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>248,888</t>
+          <t>250,789</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CVIC2603</t>
+          <t>CVIC2604</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -11128,19 +11128,19 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>250,789</t>
+          <t>252,789</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/01/2027</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>CVIC2604</t>
+          <t>CVIC2605</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -11160,29 +11160,29 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>252,789</t>
+          <t>244,567</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>26/01/2027</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CVIC2605</t>
+          <t>CVIC2606</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -11207,108 +11207,108 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>244,567</t>
+          <t>246,789</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>CVIC2606</t>
+          <t>CVIC2607</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,700</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>246,789</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CVIC2607</t>
+          <t>CVIC2608</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>221,200</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>CVIC2608</t>
+          <t>CVIC2609</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -11328,17 +11328,17 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>221,200</t>
+          <t>244,000</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -11350,49 +11350,49 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CVIC2609</t>
+          <t>CVIC2610</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>CVIC2610</t>
+          <t>CVIC2611</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11417,66 +11417,66 @@
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CVIC2611</t>
+          <t>CVJC2602</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>152,252</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>CVJC2602</t>
+          <t>CVJC2603</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11501,24 +11501,24 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>152,252</t>
+          <t>158,205</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CVJC2603</t>
+          <t>CVJC2604</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11543,66 +11543,66 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>158,205</t>
+          <t>154,606</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>CVJC2604</t>
+          <t>CVJC2605</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>154,606</t>
+          <t>132,500</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CVJC2605</t>
+          <t>CVJC2606</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -11622,17 +11622,17 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>132,500</t>
+          <t>153,500</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -11644,96 +11644,96 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>CVJC2606</t>
+          <t>CVNM2523</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>9.56 : 1</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>153,500</t>
+          <t>60,322</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CVNM2523</t>
+          <t>CVNM2601</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>9.56 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>60,322</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>CVNM2601</t>
+          <t>CVNM2603</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -11763,118 +11763,118 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CVNM2603</t>
+          <t>CVNM2605</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>CVNM2605</t>
+          <t>CVNM2606</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CVNM2606</t>
+          <t>CVNM2607</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
@@ -11884,29 +11884,29 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>CVNM2607</t>
+          <t>CVNM2608</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11916,29 +11916,29 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>66,999</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CVNM2608</t>
+          <t>CVNM2609</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -11968,24 +11968,24 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>66,999</t>
+          <t>70,111</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>CVNM2609</t>
+          <t>CVNM2613</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11995,34 +11995,34 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>2.91 : 1</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>70,111</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CVNM2613</t>
+          <t>CVNM2614</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -12032,17 +12032,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>2.91 : 1</t>
+          <t>3.88 : 1</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -12057,103 +12057,103 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>CVNM2614</t>
+          <t>CVNM2615</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>3.88 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>54,500</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CVNM2615</t>
+          <t>CVNM2616</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>54,500</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>CVNM2616</t>
+          <t>CVNM2617</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -12163,34 +12163,34 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>58,000</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CVNM2617</t>
+          <t>CVNM2618</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -12210,155 +12210,155 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>58,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>CVNM2618</t>
+          <t>CVNM2619</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CVNM2619</t>
+          <t>CVPB2528</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>37,300</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>CVPB2528</t>
+          <t>CVPB2531</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>37,300</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CVPB2531</t>
+          <t>CVPB2532</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -12388,39 +12388,39 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>CVPB2532</t>
+          <t>CVPB2603</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
@@ -12430,29 +12430,29 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CVPB2603</t>
+          <t>CVPB2606</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -12462,39 +12462,39 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>CVPB2606</t>
+          <t>CVPB2608</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -12519,66 +12519,66 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CVPB2608</t>
+          <t>CVPB2609</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3.93 : 1</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>29,476</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>CVPB2609</t>
+          <t>CVPB2610</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -12593,108 +12593,108 @@
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>29,476</t>
+          <t>28,494</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CVPB2610</t>
+          <t>CVPB2611</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>3.93 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>28,494</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>CVPB2611</t>
+          <t>CVPB2612</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>31,999</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CVPB2612</t>
+          <t>CVPB2613</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -12724,19 +12724,19 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>31,999</t>
+          <t>32,888</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>CVPB2613</t>
+          <t>CVPB2614</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12756,81 +12756,81 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>32,888</t>
+          <t>33,456</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CVPB2614</t>
+          <t>CVPB2615</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>33,456</t>
+          <t>28,500</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>CVPB2615</t>
+          <t>CVPB2616</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>28,500</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CVPB2616</t>
+          <t>CVPB2617</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -12872,17 +12872,17 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
@@ -12892,108 +12892,108 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>25,500</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>CVPB2617</t>
+          <t>CVPB2618</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>25,500</t>
+          <t>27,200</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CVPB2618</t>
+          <t>CVPB2619</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>27,200</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>CVPB2619</t>
+          <t>CVPB2620</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -13003,22 +13003,22 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -13030,7 +13030,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CVPB2620</t>
+          <t>CVPB2621</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -13065,24 +13065,24 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>CVPB2621</t>
+          <t>CVPB2622</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>25,400</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CVPB2622</t>
+          <t>CVPB2623</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -13134,17 +13134,17 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>25,400</t>
+          <t>28,600</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -13156,49 +13156,49 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>CVPB2623</t>
+          <t>CVPB2624</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>28,600</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CVPB2624</t>
+          <t>CVPB2625</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -13218,71 +13218,71 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>CVPB2625</t>
+          <t>CVRE2525</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CVRE2525</t>
+          <t>CVRE2526</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
@@ -13312,103 +13312,103 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>CVRE2526</t>
+          <t>CVRE2603</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CVRE2603</t>
+          <t>CVRE2604</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>35,999</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>CVRE2604</t>
+          <t>CVRE2605</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
@@ -13438,39 +13438,39 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>35,999</t>
+          <t>37,456</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CVRE2605</t>
+          <t>CVRE2606</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
@@ -13480,19 +13480,19 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>37,456</t>
+          <t>28,103</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>CVRE2606</t>
+          <t>CVRE2607</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -13512,17 +13512,17 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>28,103</t>
+          <t>31,870</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -13534,49 +13534,49 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CVRE2607</t>
+          <t>CVRE2608</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>31,870</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>CVRE2608</t>
+          <t>CVRE2609</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -13586,114 +13586,72 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CVRE2609</t>
+          <t>CVRE2610</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
-        <is>
-          <t>11/02/2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="inlineStr">
-        <is>
-          <t>CVRE2610</t>
-        </is>
-      </c>
-      <c r="B315" s="2" t="inlineStr">
-        <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
-        </is>
-      </c>
-      <c r="C315" s="2" t="inlineStr">
-        <is>
-          <t>8 tháng</t>
-        </is>
-      </c>
-      <c r="D315" s="2" t="inlineStr">
-        <is>
-          <t>3 : 1</t>
-        </is>
-      </c>
-      <c r="E315" s="2" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="F315" s="2" t="inlineStr">
-        <is>
-          <t>4,000,000</t>
-        </is>
-      </c>
-      <c r="G315" s="2" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="H315" s="2" t="inlineStr">
         <is>
           <t>22/04/2027</t>
         </is>

--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H314"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8662,49 +8662,49 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>CSTB2628</t>
+          <t>CSTB2627</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>24,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>81,100</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>CSTB2629</t>
+          <t>CSTB2628</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -8724,113 +8724,113 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>1,668</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>21,500,000</t>
+          <t>24,000,000</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CTCB2521</t>
+          <t>CSTB2629</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>17 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>1,668</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>21,500,000</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>42,600</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>CTCB2522</t>
+          <t>CTCB2521</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>17 tháng</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>44,500</t>
+          <t>42,600</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CTCB2523</t>
+          <t>CTCB2522</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -8860,29 +8860,29 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>45,500</t>
+          <t>44,500</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>CTCB2601</t>
+          <t>CTCB2523</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -8892,76 +8892,76 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>19,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>45,500</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>CTCB2603</t>
+          <t>CTCB2601</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VPBank ( VPX )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>19,000,000</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>CTCB2605</t>
+          <t>CTCB2603</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán VPBank ( VPX )</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -8971,202 +8971,202 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>4,700</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>CTCB2606</t>
+          <t>CTCB2605</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>4,700</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>39,500</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>CTCB2607</t>
+          <t>CTCB2606</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>3.92 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>35,259</t>
+          <t>39,500</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>CTCB2611</t>
+          <t>CTCB2607</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>3.92 : 1</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>35,259</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>CTCB2612</t>
+          <t>CTCB2611</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>CTCB2613</t>
+          <t>CTCB2612</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -9176,17 +9176,17 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -9196,39 +9196,39 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>30,500</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>CTCB2614</t>
+          <t>CTCB2613</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -9238,103 +9238,103 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>35,500</t>
+          <t>30,500</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>CTCB2615</t>
+          <t>CTCB2614</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>35,500</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>CTCB2616</t>
+          <t>CTCB2615</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>31,700</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>CTCB2617</t>
+          <t>CTCB2616</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -9354,17 +9354,17 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>35,700</t>
+          <t>31,700</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -9376,49 +9376,49 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>CTCB2618</t>
+          <t>CTCB2617</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>35,700</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>CTCB2619</t>
+          <t>CTCB2618</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9438,59 +9438,59 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>CTPB2605</t>
+          <t>CTCB2619</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -9502,22 +9502,22 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>CTPB2606</t>
+          <t>CTPB2605</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -9537,56 +9537,56 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>06/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>CTPB2607</t>
+          <t>CTPB2606</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>19,399</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>06/05/2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CTPB2608</t>
+          <t>CTPB2607</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9606,34 +9606,34 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>18,888</t>
+          <t>19,399</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>CTPB2609</t>
+          <t>CTPB2608</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9643,39 +9643,39 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>18,888</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CTPB2610</t>
+          <t>CTPB2609</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -9712,49 +9712,49 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>CTPB2611</t>
+          <t>CTPB2610</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>CTPB2612</t>
+          <t>CTPB2611</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -9774,17 +9774,17 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>CVHM2523</t>
+          <t>CTPB2612</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -9811,34 +9811,34 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>CVHM2524</t>
+          <t>CVHM2523</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9868,29 +9868,29 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>147,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>CVHM2603</t>
+          <t>CVHM2524</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9900,34 +9900,34 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>147,000</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>CVHM2604</t>
+          <t>CVHM2603</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -9937,160 +9937,160 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>4,800</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>106,000</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>CVHM2607</t>
+          <t>CVHM2604</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>135,000</t>
+          <t>106,000</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CVHM2609</t>
+          <t>CVHM2607</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>9 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>135,000</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>CVHM2610</t>
+          <t>CVHM2609</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>9 : 1</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CVHM2611</t>
+          <t>CVHM2610</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -10120,61 +10120,61 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>190,000</t>
+          <t>186,000</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>CVHM2612</t>
+          <t>CVHM2611</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>169,999</t>
+          <t>190,000</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CVHM2613</t>
+          <t>CVHM2612</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -10199,24 +10199,24 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>173,979</t>
+          <t>169,999</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>CVHM2614</t>
+          <t>CVHM2613</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -10241,108 +10241,108 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>176,868</t>
+          <t>173,979</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CVHM2615</t>
+          <t>CVHM2614</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>176,868</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>CVHM2616</t>
+          <t>CVHM2615</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>9.63 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>75,641</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CVHM2617</t>
+          <t>CVHM2616</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -10362,17 +10362,17 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>85,800</t>
+          <t>75,641</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -10384,49 +10384,49 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>CVHM2618</t>
+          <t>CVHM2617</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>9.63 : 1</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>85,800</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CVHM2619</t>
+          <t>CVHM2618</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10446,39 +10446,39 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>1,868</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>CVHM2620</t>
+          <t>CVHM2619</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10488,81 +10488,81 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,868</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CVIB2513</t>
+          <t>CVHM2620</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>76,000</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>CVIB2601</t>
+          <t>CVIB2513</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10572,76 +10572,76 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CVIB2604</t>
+          <t>CVIB2601</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>1.90 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>17,540</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>CVIB2605</t>
+          <t>CVIB2604</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1.90 : 1</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -10661,34 +10661,34 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>17,540</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CVIB2606</t>
+          <t>CVIB2605</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10698,71 +10698,71 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>17,500</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>CVIB2607</t>
+          <t>CVIB2606</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>17,500</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CVIB2608</t>
+          <t>CVIB2607</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -10782,17 +10782,17 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -10804,49 +10804,49 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>CVIB2609</t>
+          <t>CVIB2608</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>15,527</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CVIB2610</t>
+          <t>CVIB2609</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10866,39 +10866,39 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>14,613</t>
+          <t>15,527</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>CVIB2611</t>
+          <t>CVIB2610</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10908,71 +10908,71 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>13,700</t>
+          <t>14,613</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CVIC2515</t>
+          <t>CVIB2611</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>245,000</t>
+          <t>13,700</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>CVIC2516</t>
+          <t>CVIC2515</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -11002,39 +11002,39 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>245,000</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CVIC2602</t>
+          <t>CVIC2516</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -11044,19 +11044,19 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>248,888</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>CVIC2603</t>
+          <t>CVIC2602</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -11076,29 +11076,29 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>250,789</t>
+          <t>248,888</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CVIC2604</t>
+          <t>CVIC2603</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -11128,19 +11128,19 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>252,789</t>
+          <t>250,789</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>26/01/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>CVIC2605</t>
+          <t>CVIC2604</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -11160,29 +11160,29 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>244,567</t>
+          <t>252,789</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/01/2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CVIC2606</t>
+          <t>CVIC2605</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -11207,108 +11207,108 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>246,789</t>
+          <t>244,567</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>CVIC2607</t>
+          <t>CVIC2606</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>246,789</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CVIC2608</t>
+          <t>CVIC2607</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,700</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>221,200</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>CVIC2609</t>
+          <t>CVIC2608</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -11328,17 +11328,17 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>221,200</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -11350,49 +11350,49 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CVIC2610</t>
+          <t>CVIC2609</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>244,000</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>CVIC2611</t>
+          <t>CVIC2610</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11417,66 +11417,66 @@
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CVJC2602</t>
+          <t>CVIC2611</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>152,252</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>CVJC2603</t>
+          <t>CVJC2602</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11501,24 +11501,24 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>158,205</t>
+          <t>152,252</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CVJC2604</t>
+          <t>CVJC2603</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11543,66 +11543,66 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>154,606</t>
+          <t>158,205</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>CVJC2605</t>
+          <t>CVJC2604</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>132,500</t>
+          <t>154,606</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CVJC2606</t>
+          <t>CVJC2605</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -11622,17 +11622,17 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>153,500</t>
+          <t>132,500</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -11644,96 +11644,96 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>CVNM2523</t>
+          <t>CVJC2606</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>9.56 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>60,322</t>
+          <t>153,500</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CVNM2601</t>
+          <t>CVNM2523</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>9.56 : 1</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>60,322</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>CVNM2603</t>
+          <t>CVNM2601</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -11763,118 +11763,118 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CVNM2605</t>
+          <t>CVNM2603</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>CVNM2606</t>
+          <t>CVNM2605</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CVNM2607</t>
+          <t>CVNM2606</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
@@ -11884,29 +11884,29 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>CVNM2608</t>
+          <t>CVNM2607</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11916,29 +11916,29 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>66,999</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CVNM2609</t>
+          <t>CVNM2608</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -11968,24 +11968,24 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>70,111</t>
+          <t>66,999</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>CVNM2613</t>
+          <t>CVNM2609</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11995,34 +11995,34 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>2.91 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>70,111</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CVNM2614</t>
+          <t>CVNM2613</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -12032,17 +12032,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>3.88 : 1</t>
+          <t>2.91 : 1</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -12057,103 +12057,103 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>CVNM2615</t>
+          <t>CVNM2614</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3.88 : 1</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>54,500</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CVNM2616</t>
+          <t>CVNM2615</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>54,500</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>CVNM2617</t>
+          <t>CVNM2616</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -12163,34 +12163,34 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>58,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CVNM2618</t>
+          <t>CVNM2617</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -12210,155 +12210,155 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>58,000</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>CVNM2619</t>
+          <t>CVNM2618</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CVPB2528</t>
+          <t>CVNM2619</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>37,300</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>CVPB2531</t>
+          <t>CVPB2528</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>37,300</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CVPB2532</t>
+          <t>CVPB2531</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -12388,39 +12388,39 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>CVPB2603</t>
+          <t>CVPB2532</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
@@ -12430,29 +12430,29 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CVPB2606</t>
+          <t>CVPB2603</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -12462,39 +12462,39 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>CVPB2608</t>
+          <t>CVPB2606</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -12519,66 +12519,66 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CVPB2609</t>
+          <t>CVPB2608</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>3.93 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>29,476</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>CVPB2610</t>
+          <t>CVPB2609</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -12593,108 +12593,108 @@
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>28,494</t>
+          <t>29,476</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CVPB2611</t>
+          <t>CVPB2610</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3.93 : 1</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>28,494</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>CVPB2612</t>
+          <t>CVPB2611</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>31,999</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CVPB2613</t>
+          <t>CVPB2612</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -12724,19 +12724,19 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>32,888</t>
+          <t>31,999</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>CVPB2614</t>
+          <t>CVPB2613</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12756,81 +12756,81 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>33,456</t>
+          <t>32,888</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CVPB2615</t>
+          <t>CVPB2614</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>28,500</t>
+          <t>33,456</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>CVPB2616</t>
+          <t>CVPB2615</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>28,500</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CVPB2617</t>
+          <t>CVPB2616</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -12872,17 +12872,17 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
@@ -12892,108 +12892,108 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>25,500</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>CVPB2618</t>
+          <t>CVPB2617</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>27,200</t>
+          <t>25,500</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CVPB2619</t>
+          <t>CVPB2618</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,200</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>CVPB2620</t>
+          <t>CVPB2619</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -13003,22 +13003,22 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -13030,7 +13030,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CVPB2621</t>
+          <t>CVPB2620</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -13065,24 +13065,24 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>CVPB2622</t>
+          <t>CVPB2621</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>25,400</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CVPB2623</t>
+          <t>CVPB2622</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -13134,17 +13134,17 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>28,600</t>
+          <t>25,400</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -13156,49 +13156,49 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>CVPB2624</t>
+          <t>CVPB2623</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>28,600</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CVPB2625</t>
+          <t>CVPB2624</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -13218,71 +13218,71 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>CVRE2525</t>
+          <t>CVPB2625</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CVRE2526</t>
+          <t>CVRE2525</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
@@ -13312,103 +13312,103 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>CVRE2603</t>
+          <t>CVRE2526</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CVRE2604</t>
+          <t>CVRE2603</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>35,999</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>CVRE2605</t>
+          <t>CVRE2604</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
@@ -13438,39 +13438,39 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>37,456</t>
+          <t>35,999</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CVRE2606</t>
+          <t>CVRE2605</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
@@ -13480,19 +13480,19 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>28,103</t>
+          <t>37,456</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>CVRE2607</t>
+          <t>CVRE2606</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -13512,17 +13512,17 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>31,870</t>
+          <t>28,103</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -13534,49 +13534,49 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CVRE2608</t>
+          <t>CVRE2607</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>31,870</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>CVRE2609</t>
+          <t>CVRE2608</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -13586,72 +13586,114 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
+          <t>CVRE2609</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>6 tháng</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>2,468</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>11,000,000</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>23,000</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>11/02/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
           <t>CVRE2610</t>
         </is>
       </c>
-      <c r="B314" s="2" t="inlineStr">
+      <c r="B315" s="2" t="inlineStr">
         <is>
           <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
-      <c r="C314" s="2" t="inlineStr">
+      <c r="C315" s="2" t="inlineStr">
         <is>
           <t>8 tháng</t>
         </is>
       </c>
-      <c r="D314" s="2" t="inlineStr">
+      <c r="D315" s="2" t="inlineStr">
         <is>
           <t>3 : 1</t>
         </is>
       </c>
-      <c r="E314" s="2" t="inlineStr">
+      <c r="E315" s="2" t="inlineStr">
         <is>
           <t>2,400</t>
         </is>
       </c>
-      <c r="F314" s="2" t="inlineStr">
+      <c r="F315" s="2" t="inlineStr">
         <is>
           <t>4,000,000</t>
         </is>
       </c>
-      <c r="G314" s="2" t="inlineStr">
+      <c r="G315" s="2" t="inlineStr">
         <is>
           <t>25,000</t>
         </is>
       </c>
-      <c r="H314" s="2" t="inlineStr">
+      <c r="H315" s="2" t="inlineStr">
         <is>
           <t>22/04/2027</t>
         </is>

--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H340"/>
+  <dimension ref="A1:H337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10006,17 +10006,17 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CTCB2621</t>
+          <t>CTPB2605</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -10026,76 +10026,76 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>5,700</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>CTCB2622</t>
+          <t>CTPB2606</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>06/05/2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CTCB2623</t>
+          <t>CTPB2607</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10105,101 +10105,101 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>39,500</t>
+          <t>19,399</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>CTPB2605</t>
+          <t>CTPB2608</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>18,888</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CTPB2606</t>
+          <t>CTPB2609</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -10209,34 +10209,34 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>06/05/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>CTPB2607</t>
+          <t>CTPB2610</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -10246,29 +10246,29 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>19,399</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CTPB2608</t>
+          <t>CTPB2611</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -10278,91 +10278,91 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>18,888</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>CTPB2609</t>
+          <t>CTPB2612</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CTPB2610</t>
+          <t>CVHM2523</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -10372,19 +10372,19 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>CTPB2611</t>
+          <t>CVHM2524</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -10394,44 +10394,44 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>147,000</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CTPB2612</t>
+          <t>CVHM2603</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10441,39 +10441,39 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>4,800</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>CVHM2523</t>
+          <t>CVHM2604</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10483,86 +10483,86 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>106,000</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CVHM2524</t>
+          <t>CVHM2609</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>9 : 1</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>147,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>CVHM2603</t>
+          <t>CVHM2610</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10572,118 +10572,118 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>186,000</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CVHM2604</t>
+          <t>CVHM2611</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>106,000</t>
+          <t>190,000</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>CVHM2609</t>
+          <t>CVHM2613</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>9 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>173,979</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CVHM2610</t>
+          <t>CVHM2614</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10693,165 +10693,165 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>176,868</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>CVHM2611</t>
+          <t>CVHM2615</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>190,000</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CVHM2613</t>
+          <t>CVHM2616</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>9.63 : 1</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>173,979</t>
+          <t>75,641</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>CVHM2614</t>
+          <t>CVHM2617</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>9.63 : 1</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>176,868</t>
+          <t>85,800</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CVHM2615</t>
+          <t>CVHM2618</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10861,91 +10861,91 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>CVHM2616</t>
+          <t>CVHM2619</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>9.63 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>1,868</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>75,641</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CVHM2617</t>
+          <t>CVHM2620</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>9.63 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -10955,34 +10955,34 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>85,800</t>
+          <t>76,000</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>CVHM2618</t>
+          <t>CVHM2621</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10992,39 +10992,39 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CVHM2619</t>
+          <t>CVHM2622</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -11034,165 +11034,165 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>1,868</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>77,000</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>CVHM2620</t>
+          <t>CVIB2513</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CVHM2621</t>
+          <t>CVIB2601</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>CVHM2622</t>
+          <t>CVIB2604</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>1.90 : 1</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>77,000</t>
+          <t>17,540</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CVIB2513</t>
+          <t>CVIB2605</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -11202,39 +11202,39 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>CVIB2601</t>
+          <t>CVIB2606</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11244,449 +11244,449 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>17,500</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CVIB2604</t>
+          <t>CVIB2607</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>1.90 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>17,540</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>CVIB2605</t>
+          <t>CVIB2608</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CVIB2606</t>
+          <t>CVIB2609</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>17,500</t>
+          <t>15,527</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>CVIB2607</t>
+          <t>CVIB2610</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>14,613</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CVIB2608</t>
+          <t>CVIB2611</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>13,700</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>CVIB2609</t>
+          <t>CVIC2515</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>15,527</t>
+          <t>245,000</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CVIB2610</t>
+          <t>CVIC2516</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>14,613</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>CVIB2611</t>
+          <t>CVIC2602</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>13,700</t>
+          <t>248,888</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CVIC2515</t>
+          <t>CVIC2603</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>245,000</t>
+          <t>250,789</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>CVIC2516</t>
+          <t>CVIC2604</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>252,789</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>26/01/2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CVIC2602</t>
+          <t>CVIC2606</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -11711,76 +11711,76 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>248,888</t>
+          <t>246,789</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>CVIC2603</t>
+          <t>CVIC2607</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,700</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>250,789</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CVIC2604</t>
+          <t>CVIC2608</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
@@ -11800,29 +11800,29 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>252,789</t>
+          <t>221,200</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>26/01/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>CVIC2606</t>
+          <t>CVIC2609</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -11842,24 +11842,24 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>246,789</t>
+          <t>244,000</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CVIC2607</t>
+          <t>CVIC2610</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11869,17 +11869,17 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -11889,108 +11889,108 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>CVIC2608</t>
+          <t>CVIC2611</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>221,200</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CVIC2609</t>
+          <t>CVIC2612</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>6,200</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>248,000</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>CVIC2610</t>
+          <t>CVIC2613</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -12000,39 +12000,39 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>8,400</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>224,000</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CVIC2611</t>
+          <t>CVIC2614</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -12042,286 +12042,286 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>8,300</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>248,000</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>CVIC2612</t>
+          <t>CVJC2602</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>6,200</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>248,000</t>
+          <t>152,252</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CVIC2613</t>
+          <t>CVJC2603</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>224,000</t>
+          <t>158,205</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>CVIC2614</t>
+          <t>CVJC2604</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>8,300</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>248,000</t>
+          <t>154,606</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CVJC2602</t>
+          <t>CVJC2605</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>152,252</t>
+          <t>132,500</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>CVJC2603</t>
+          <t>CVJC2606</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>158,205</t>
+          <t>153,500</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CVJC2604</t>
+          <t>CVNM2523</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>9.56 : 1</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>154,606</t>
+          <t>60,322</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>CVJC2605</t>
+          <t>CVNM2601</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12331,39 +12331,39 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>132,500</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CVJC2606</t>
+          <t>CVNM2603</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12373,333 +12373,333 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>153,500</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>CVNM2523</t>
+          <t>CVNM2605</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>9.56 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>60,322</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CVNM2601</t>
+          <t>CVNM2606</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>CVNM2603</t>
+          <t>CVNM2607</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CVNM2605</t>
+          <t>CVNM2609</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>70,111</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>CVNM2606</t>
+          <t>CVNM2613</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>2.91 : 1</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CVNM2607</t>
+          <t>CVNM2614</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>3.88 : 1</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>CVNM2609</t>
+          <t>CVNM2615</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>70,111</t>
+          <t>54,500</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CVNM2613</t>
+          <t>CVNM2616</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -12709,86 +12709,86 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>2.91 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>CVNM2614</t>
+          <t>CVNM2617</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>3.88 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>58,000</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CVNM2615</t>
+          <t>CVNM2618</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -12798,259 +12798,259 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>54,500</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>CVNM2616</t>
+          <t>CVNM2619</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CVNM2617</t>
+          <t>CVNM2620</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>13,000,000</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>58,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>CVNM2618</t>
+          <t>CVNM2621</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CVNM2619</t>
+          <t>CVNM2622</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>4,300</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>CVNM2620</t>
+          <t>CVNM2623</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>13,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CVNM2621</t>
+          <t>CVPB2528</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>37,300</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>CVNM2622</t>
+          <t>CVPB2531</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -13092,244 +13092,244 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CVNM2623</t>
+          <t>CVPB2532</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>CVPB2528</t>
+          <t>CVPB2603</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>37,300</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CVPB2531</t>
+          <t>CVPB2608</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>CVPB2532</t>
+          <t>CVPB2609</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3.93 : 1</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>29,476</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CVPB2603</t>
+          <t>CVPB2610</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3.93 : 1</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>28,494</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>CVPB2608</t>
+          <t>CVPB2611</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -13339,165 +13339,165 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CVPB2609</t>
+          <t>CVPB2613</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>3.93 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>29,476</t>
+          <t>32,888</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>CVPB2610</t>
+          <t>CVPB2614</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>3.93 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>28,494</t>
+          <t>33,456</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CVPB2611</t>
+          <t>CVPB2615</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>28,500</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>CVPB2613</t>
+          <t>CVPB2616</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -13507,86 +13507,86 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>32,888</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CVPB2614</t>
+          <t>CVPB2617</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>33,456</t>
+          <t>25,500</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>CVPB2615</t>
+          <t>CVPB2618</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
@@ -13596,34 +13596,34 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>28,500</t>
+          <t>27,200</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CVPB2616</t>
+          <t>CVPB2619</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -13633,170 +13633,170 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>CVPB2617</t>
+          <t>CVPB2620</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>25,500</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CVPB2618</t>
+          <t>CVPB2621</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>27,200</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>CVPB2619</t>
+          <t>CVPB2622</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>25,400</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CVPB2620</t>
+          <t>CVPB2623</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -13806,34 +13806,34 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>28,600</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>CVPB2621</t>
+          <t>CVPB2624</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -13843,716 +13843,716 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CVPB2622</t>
+          <t>CVPB2625</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>25,400</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>CVPB2623</t>
+          <t>CVPB2626</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>28,600</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CVPB2624</t>
+          <t>CVPB2627</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>4,600</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>CVPB2625</t>
+          <t>CVPB2628</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>4,100</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CVPB2626</t>
+          <t>CVPB2629</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1.59 : 1</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>25,064</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>CVPB2627</t>
+          <t>CVRE2525</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>4,600</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CVPB2628</t>
+          <t>CVRE2526</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>CVPB2629</t>
+          <t>CVRE2603</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>1.59 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>25,064</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CVRE2525</t>
+          <t>CVRE2604</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>35,999</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>CVRE2526</t>
+          <t>CVRE2605</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>37,456</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CVRE2603</t>
+          <t>CVRE2606</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>28,103</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>CVRE2604</t>
+          <t>CVRE2607</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>35,999</t>
+          <t>31,870</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CVRE2605</t>
+          <t>CVRE2608</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>37,456</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>CVRE2606</t>
+          <t>CVRE2609</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>28,103</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CVRE2607</t>
+          <t>CVRE2610</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>31,870</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>CVRE2608</t>
+          <t>CVRE2611</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CVRE2609</t>
+          <t>CVRE2612</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
@@ -14562,188 +14562,62 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>4,600</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>CVRE2610</t>
+          <t>CVRE2613</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>4,600</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>CVRE2611</t>
-        </is>
-      </c>
-      <c r="B338" s="2" t="inlineStr">
-        <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
-        </is>
-      </c>
-      <c r="C338" s="2" t="inlineStr">
-        <is>
-          <t>4 tháng</t>
-        </is>
-      </c>
-      <c r="D338" s="2" t="inlineStr">
-        <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="E338" s="2" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
-      <c r="F338" s="2" t="inlineStr">
-        <is>
-          <t>8,000,000</t>
-        </is>
-      </c>
-      <c r="G338" s="2" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="H338" s="2" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>CVRE2612</t>
-        </is>
-      </c>
-      <c r="B339" s="2" t="inlineStr">
-        <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
-        </is>
-      </c>
-      <c r="C339" s="2" t="inlineStr">
-        <is>
-          <t>5 tháng</t>
-        </is>
-      </c>
-      <c r="D339" s="2" t="inlineStr">
-        <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="E339" s="2" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
-      <c r="F339" s="2" t="inlineStr">
-        <is>
-          <t>8,000,000</t>
-        </is>
-      </c>
-      <c r="G339" s="2" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="H339" s="2" t="inlineStr">
-        <is>
-          <t>09/02/2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>CVRE2613</t>
-        </is>
-      </c>
-      <c r="B340" s="2" t="inlineStr">
-        <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
-        </is>
-      </c>
-      <c r="C340" s="2" t="inlineStr">
-        <is>
-          <t>7 tháng</t>
-        </is>
-      </c>
-      <c r="D340" s="2" t="inlineStr">
-        <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
-      <c r="F340" s="2" t="inlineStr">
-        <is>
-          <t>7,000,000</t>
-        </is>
-      </c>
-      <c r="G340" s="2" t="inlineStr">
-        <is>
-          <t>27,000</t>
-        </is>
-      </c>
-      <c r="H340" s="2" t="inlineStr">
         <is>
           <t>01/04/2027</t>
         </is>

--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10006,17 +10006,17 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CTPB2605</t>
+          <t>CTCB2621</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -10026,76 +10026,76 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>5,700</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>CTPB2606</t>
+          <t>CTCB2622</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>06/05/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CTPB2607</t>
+          <t>CTCB2623</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10105,101 +10105,101 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>19,399</t>
+          <t>39,500</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>CTPB2608</t>
+          <t>CTPB2605</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>18,888</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CTPB2609</t>
+          <t>CTPB2606</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -10209,34 +10209,34 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>06/05/2027</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>CTPB2610</t>
+          <t>CTPB2607</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -10246,29 +10246,29 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>19,399</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CTPB2611</t>
+          <t>CTPB2608</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -10278,91 +10278,91 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>18,888</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>CTPB2612</t>
+          <t>CTPB2609</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CVHM2523</t>
+          <t>CTPB2610</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -10372,19 +10372,19 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>CVHM2524</t>
+          <t>CTPB2611</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -10394,44 +10394,44 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>147,000</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CVHM2603</t>
+          <t>CTPB2612</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10441,39 +10441,39 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>CVHM2604</t>
+          <t>CVHM2523</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10483,86 +10483,86 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>106,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CVHM2609</t>
+          <t>CVHM2524</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>9 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>147,000</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>CVHM2610</t>
+          <t>CVHM2603</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10572,118 +10572,118 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>4,800</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CVHM2611</t>
+          <t>CVHM2604</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>190,000</t>
+          <t>106,000</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>CVHM2613</t>
+          <t>CVHM2609</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>9 : 1</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>173,979</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CVHM2614</t>
+          <t>CVHM2610</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10693,165 +10693,165 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>176,868</t>
+          <t>186,000</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>CVHM2615</t>
+          <t>CVHM2611</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>190,000</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CVHM2616</t>
+          <t>CVHM2613</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>9.63 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>75,641</t>
+          <t>173,979</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>CVHM2617</t>
+          <t>CVHM2614</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>9.63 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>85,800</t>
+          <t>176,868</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CVHM2618</t>
+          <t>CVHM2615</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10861,91 +10861,91 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>CVHM2619</t>
+          <t>CVHM2616</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>9.63 : 1</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>1,868</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>75,641</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CVHM2620</t>
+          <t>CVHM2617</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>9.63 : 1</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -10955,34 +10955,34 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>85,800</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>CVHM2621</t>
+          <t>CVHM2618</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10992,39 +10992,39 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CVHM2622</t>
+          <t>CVHM2619</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -11034,165 +11034,165 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>1,868</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>77,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>CVIB2513</t>
+          <t>CVHM2620</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>76,000</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CVIB2601</t>
+          <t>CVHM2621</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>CVIB2604</t>
+          <t>CVHM2622</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>1.90 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>17,540</t>
+          <t>77,000</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CVIB2605</t>
+          <t>CVIB2513</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -11202,39 +11202,39 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>CVIB2606</t>
+          <t>CVIB2601</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11244,449 +11244,449 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>17,500</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CVIB2607</t>
+          <t>CVIB2604</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>1.90 : 1</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>17,540</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>CVIB2608</t>
+          <t>CVIB2605</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CVIB2609</t>
+          <t>CVIB2606</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>15,527</t>
+          <t>17,500</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>CVIB2610</t>
+          <t>CVIB2607</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>14,613</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CVIB2611</t>
+          <t>CVIB2608</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>1.83 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>13,700</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>CVIC2515</t>
+          <t>CVIB2609</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>245,000</t>
+          <t>15,527</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CVIC2516</t>
+          <t>CVIB2610</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>14,613</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>CVIC2602</t>
+          <t>CVIB2611</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>1.83 : 1</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>248,888</t>
+          <t>13,700</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CVIC2603</t>
+          <t>CVIC2515</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>250,789</t>
+          <t>245,000</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>CVIC2604</t>
+          <t>CVIC2516</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>252,789</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>26/01/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CVIC2606</t>
+          <t>CVIC2602</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -11711,76 +11711,76 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>246,789</t>
+          <t>248,888</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>CVIC2607</t>
+          <t>CVIC2603</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>250,789</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CVIC2608</t>
+          <t>CVIC2604</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
@@ -11800,29 +11800,29 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>221,200</t>
+          <t>252,789</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>26/01/2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>CVIC2609</t>
+          <t>CVIC2606</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -11842,24 +11842,24 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>246,789</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CVIC2610</t>
+          <t>CVIC2607</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11869,17 +11869,17 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>3,700</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -11889,108 +11889,108 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>CVIC2611</t>
+          <t>CVIC2608</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>221,200</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CVIC2612</t>
+          <t>CVIC2609</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>6,200</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>248,000</t>
+          <t>244,000</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>CVIC2613</t>
+          <t>CVIC2610</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -12000,39 +12000,39 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>224,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CVIC2614</t>
+          <t>CVIC2611</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -12042,286 +12042,286 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>8,300</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>248,000</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>CVJC2602</t>
+          <t>CVIC2612</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>6,200</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>152,252</t>
+          <t>248,000</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CVJC2603</t>
+          <t>CVIC2613</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>8,400</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>158,205</t>
+          <t>224,000</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>CVJC2604</t>
+          <t>CVIC2614</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>8,300</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>154,606</t>
+          <t>248,000</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CVJC2605</t>
+          <t>CVJC2602</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>132,500</t>
+          <t>152,252</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>CVJC2606</t>
+          <t>CVJC2603</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>153,500</t>
+          <t>158,205</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CVNM2523</t>
+          <t>CVJC2604</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>9.56 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>60,322</t>
+          <t>154,606</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>CVNM2601</t>
+          <t>CVJC2605</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12331,39 +12331,39 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>132,500</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CVNM2603</t>
+          <t>CVJC2606</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12373,333 +12373,333 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>153,500</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>CVNM2605</t>
+          <t>CVNM2523</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>9.56 : 1</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>60,322</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CVNM2606</t>
+          <t>CVNM2601</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>CVNM2607</t>
+          <t>CVNM2603</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CVNM2609</t>
+          <t>CVNM2605</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>70,111</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>CVNM2613</t>
+          <t>CVNM2606</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>2.91 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CVNM2614</t>
+          <t>CVNM2607</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>3.88 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>CVNM2615</t>
+          <t>CVNM2609</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>54,500</t>
+          <t>70,111</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CVNM2616</t>
+          <t>CVNM2613</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -12709,86 +12709,86 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>2.91 : 1</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>CVNM2617</t>
+          <t>CVNM2614</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3.88 : 1</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>58,000</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CVNM2618</t>
+          <t>CVNM2615</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -12798,259 +12798,259 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>54,500</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>CVNM2619</t>
+          <t>CVNM2616</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CVNM2620</t>
+          <t>CVNM2617</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>13,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>58,000</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>CVNM2621</t>
+          <t>CVNM2618</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CVNM2622</t>
+          <t>CVNM2619</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>CVNM2623</t>
+          <t>CVNM2620</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>13,000,000</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CVPB2528</t>
+          <t>CVNM2621</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>37,300</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>CVPB2531</t>
+          <t>CVNM2622</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -13092,244 +13092,244 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>4,300</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CVPB2532</t>
+          <t>CVNM2623</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>CVPB2603</t>
+          <t>CVPB2528</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>37,300</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CVPB2608</t>
+          <t>CVPB2531</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>CVPB2609</t>
+          <t>CVPB2532</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>3.93 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>29,476</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CVPB2610</t>
+          <t>CVPB2603</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>3.93 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>28,494</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>CVPB2611</t>
+          <t>CVPB2608</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -13339,165 +13339,165 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CVPB2613</t>
+          <t>CVPB2609</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3.93 : 1</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>32,888</t>
+          <t>29,476</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>CVPB2614</t>
+          <t>CVPB2610</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3.93 : 1</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>33,456</t>
+          <t>28,494</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CVPB2615</t>
+          <t>CVPB2611</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>28,500</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>CVPB2616</t>
+          <t>CVPB2613</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -13507,86 +13507,86 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>32,888</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CVPB2617</t>
+          <t>CVPB2614</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>25,500</t>
+          <t>33,456</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>CVPB2618</t>
+          <t>CVPB2615</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
@@ -13596,34 +13596,34 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>27,200</t>
+          <t>28,500</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CVPB2619</t>
+          <t>CVPB2616</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -13633,170 +13633,170 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>CVPB2620</t>
+          <t>CVPB2617</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>25,500</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CVPB2621</t>
+          <t>CVPB2618</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>27,200</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>CVPB2622</t>
+          <t>CVPB2619</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>25,400</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CVPB2623</t>
+          <t>CVPB2620</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -13806,34 +13806,34 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>28,600</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>CVPB2624</t>
+          <t>CVPB2621</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -13843,716 +13843,716 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CVPB2625</t>
+          <t>CVPB2622</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>25,400</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>CVPB2626</t>
+          <t>CVPB2623</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>28,600</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CVPB2627</t>
+          <t>CVPB2624</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>4,600</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>CVPB2628</t>
+          <t>CVPB2625</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CVPB2629</t>
+          <t>CVPB2626</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>1.59 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>25,064</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>CVRE2525</t>
+          <t>CVPB2627</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>4,600</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CVRE2526</t>
+          <t>CVPB2628</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>4,100</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>CVRE2603</t>
+          <t>CVPB2629</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>1.59 : 1</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>25,064</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CVRE2604</t>
+          <t>CVRE2525</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>35,999</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>CVRE2605</t>
+          <t>CVRE2526</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>37,456</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CVRE2606</t>
+          <t>CVRE2603</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>28,103</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>CVRE2607</t>
+          <t>CVRE2604</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>31,870</t>
+          <t>35,999</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CVRE2608</t>
+          <t>CVRE2605</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>37,456</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>CVRE2609</t>
+          <t>CVRE2606</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>28,103</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CVRE2610</t>
+          <t>CVRE2607</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>31,870</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>CVRE2611</t>
+          <t>CVRE2608</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CVRE2612</t>
+          <t>CVRE2609</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
@@ -14562,62 +14562,188 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>4,600</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
+          <t>CVRE2610</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>8 tháng</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>3 : 1</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>4,000,000</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>22/04/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>CVRE2611</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>4 tháng</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>8,000,000</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>CVRE2612</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>5 tháng</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>8,000,000</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>09/02/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
           <t>CVRE2613</t>
         </is>
       </c>
-      <c r="B337" s="2" t="inlineStr">
+      <c r="B340" s="2" t="inlineStr">
         <is>
           <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
-      <c r="C337" s="2" t="inlineStr">
+      <c r="C340" s="2" t="inlineStr">
         <is>
           <t>7 tháng</t>
         </is>
       </c>
-      <c r="D337" s="2" t="inlineStr">
+      <c r="D340" s="2" t="inlineStr">
         <is>
           <t>2 : 1</t>
         </is>
       </c>
-      <c r="E337" s="2" t="inlineStr">
+      <c r="E340" s="2" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="F337" s="2" t="inlineStr">
+      <c r="F340" s="2" t="inlineStr">
         <is>
           <t>7,000,000</t>
         </is>
       </c>
-      <c r="G337" s="2" t="inlineStr">
+      <c r="G340" s="2" t="inlineStr">
         <is>
           <t>27,000</t>
         </is>
       </c>
-      <c r="H337" s="2" t="inlineStr">
+      <c r="H340" s="2" t="inlineStr">
         <is>
           <t>01/04/2027</t>
         </is>

--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H334"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -808,7 +808,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CACB2609</t>
+          <t>CACB2610</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -838,150 +838,150 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,909</t>
+          <t>25,964</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CACB2610</t>
+          <t>CACB2614</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4.31 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,964</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CACB2614</t>
+          <t>CACB2615</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CACB2615</t>
+          <t>CACB2616</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,200</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>23,500</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CACB2616</t>
+          <t>CACB2617</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -991,22 +991,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,500</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CACB2617</t>
+          <t>CACB2618</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1048,29 +1048,29 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>23,500</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CACB2618</t>
+          <t>CACB2619</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1080,29 +1080,29 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,868</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,500</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CACB2619</t>
+          <t>CACB2620</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1112,59 +1112,59 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,868</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CACB2620</t>
+          <t>CACB2621</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1174,19 +1174,19 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CACB2621</t>
+          <t>CACB2622</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1206,29 +1206,29 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>3,800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CACB2622</t>
+          <t>CACB2623</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>24,000</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CACB2623</t>
+          <t>CACB2624</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1290,160 +1290,160 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>25,300</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CACB2624</t>
+          <t>CFPT2529</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>17 tháng</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>4,700</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,300</t>
+          <t>106,900</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CFPT2529</t>
+          <t>CFPT2533</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>17 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4,700</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>106,900</t>
+          <t>106,000</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CFPT2533</t>
+          <t>CFPT2603</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>106,000</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CFPT2603</t>
+          <t>CFPT2604</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1458,34 +1458,34 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,300</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CFPT2604</t>
+          <t>CFPT2609</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1495,118 +1495,118 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>16 : 1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>98,500</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CFPT2609</t>
+          <t>CFPT2610</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>19,000,000</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,500</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CFPT2610</t>
+          <t>CFPT2611</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CFPT2611</t>
+          <t>CFPT2612</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>23 : 1</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1636,61 +1636,61 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>81,000</t>
+          <t>77,000</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CFPT2612</t>
+          <t>CFPT2613</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>23 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>77,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CFPT2613</t>
+          <t>CFPT2614</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1720,34 +1720,34 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CFPT2614</t>
+          <t>CFPT2615</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>9.86 : 1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1757,155 +1757,155 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>73,981</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CFPT2615</t>
+          <t>CFPT2617</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>9.86 : 1</t>
+          <t>16 : 1</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>73,981</t>
+          <t>85,678</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CFPT2616</t>
+          <t>CFPT2621</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>16 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>82,456</t>
+          <t>70,500</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CFPT2617</t>
+          <t>CFPT2622</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>16 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>85,678</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CFPT2621</t>
+          <t>CFPT2623</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1930,39 +1930,39 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>70,500</t>
+          <t>70,100</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>28/12/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CFPT2622</t>
+          <t>CFPT2624</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>77,000</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CFPT2623</t>
+          <t>CFPT2625</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1999,49 +1999,49 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>70,100</t>
+          <t>74,000</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CFPT2624</t>
+          <t>CFPT2626</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2051,34 +2051,34 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>77,000</t>
+          <t>74,500</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CFPT2625</t>
+          <t>CFPT2627</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2093,34 +2093,34 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>74,000</t>
+          <t>68,700</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CFPT2626</t>
+          <t>CFPT2628</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2130,239 +2130,239 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>74,500</t>
+          <t>75,800</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CFPT2627</t>
+          <t>CFPT2629</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>68,700</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CFPT2628</t>
+          <t>CFPT2630</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>19,000,000</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>75,800</t>
+          <t>76,000</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CFPT2629</t>
+          <t>CFPT2631</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CFPT2630</t>
+          <t>CFPT2632</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3.64 : 1</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>19,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>65,473</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CFPT2631</t>
+          <t>CFPT2633</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>3.64 : 1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>62,745</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CFPT2632</t>
+          <t>CFPT2634</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2382,76 +2382,76 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>65,473</t>
+          <t>69,110</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CFPT2633</t>
+          <t>CFPT2635</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3.64 : 1</t>
+          <t>7.27 : 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>5,800</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>62,745</t>
+          <t>73,657</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CFPT2634</t>
+          <t>CFPT2636</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2461,81 +2461,81 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3.64 : 1</t>
+          <t>9 : 1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>69,110</t>
+          <t>69,100</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>21/04/2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CFPT2635</t>
+          <t>CFPT2637</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>7.27 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>73,657</t>
+          <t>75,200</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>CFPT2636</t>
+          <t>CFPT2638</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2545,27 +2545,27 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>9 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>69,100</t>
+          <t>75,200</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2027</t>
+          <t>03/05/2027</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CHDB2606</t>
+          <t>CHDB2607</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2770,61 +2770,61 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>29,999</t>
+          <t>31,999</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>CHDB2607</t>
+          <t>CHDB2608</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>31,999</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/12/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>CHDB2608</t>
+          <t>CHDB2609</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2854,66 +2854,66 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>26,300</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CHDB2609</t>
+          <t>CHDB2610</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>26,300</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>CHDB2610</t>
+          <t>CHDB2611</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2950,49 +2950,49 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CHDB2611</t>
+          <t>CHDB2612</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>24,100</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>CHDB2612</t>
+          <t>CHDB2613</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>24,100</t>
+          <t>27,200</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3034,49 +3034,49 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CHDB2613</t>
+          <t>CHDB2614</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>27,200</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>CHDB2614</t>
+          <t>CHDB2615</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3096,39 +3096,39 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>CHDB2615</t>
+          <t>CHPG2539</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>17 tháng</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3138,81 +3138,81 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>34,300</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>CHPG2539</t>
+          <t>CHPG2541</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>17 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>34,300</t>
+          <t>33,000</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>CHPG2541</t>
+          <t>CHPG2603</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3222,34 +3222,34 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>33,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>CHPG2603</t>
+          <t>CHPG2605</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3259,39 +3259,39 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>CHPG2605</t>
+          <t>CHPG2606</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán VPBank ( VPX )</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3301,39 +3301,39 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/12/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>CHPG2606</t>
+          <t>CHPG2609</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VPBank ( VPX )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3343,39 +3343,39 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>CHPG2609</t>
+          <t>CHPG2610</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3390,86 +3390,86 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>29,500</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>12/01/2027</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>CHPG2610</t>
+          <t>CHPG2613</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>4.46 : 1</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>29,500</t>
+          <t>26,778</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>12/01/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>CHPG2613</t>
+          <t>CHPG2614</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>4.46 : 1</t>
+          <t>3.57 : 1</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>26,778</t>
+          <t>25,439</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>CHPG2614</t>
+          <t>CHPG2615</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3526,61 +3526,61 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>25,439</t>
+          <t>25,885</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>CHPG2615</t>
+          <t>CHPG2616</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>3.57 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>25,885</t>
+          <t>24,100</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>CHPG2616</t>
+          <t>CHPG2617</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3610,29 +3610,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>24,100</t>
+          <t>25,400</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>CHPG2617</t>
+          <t>CHPG2618</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3642,29 +3642,29 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>25,400</t>
+          <t>28,888</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>CHPG2618</t>
+          <t>CHPG2619</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3694,113 +3694,113 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>28,888</t>
+          <t>28,333</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>CHPG2619</t>
+          <t>CHPG2625</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>28,333</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>CHPG2621</t>
+          <t>CHPG2626</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>27,999</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>CHPG2625</t>
+          <t>CHPG2627</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3810,39 +3810,39 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>23,500</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>CHPG2626</t>
+          <t>CHPG2628</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3852,34 +3852,34 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>4,100</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>24,600</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>CHPG2627</t>
+          <t>CHPG2629</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3889,328 +3889,328 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>23,500</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>CHPG2628</t>
+          <t>CHPG2630</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KB Việt Nam ( KBSV )</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>24,600</t>
+          <t>25,300</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>04/05/2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>CHPG2629</t>
+          <t>CHPG2631</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>24,500</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>CHPG2630</t>
+          <t>CHPG2632</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KB Việt Nam ( KBSV )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>25,300</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>04/05/2027</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>CHPG2631</t>
+          <t>CHPG2633</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>24,000,000</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>24,500</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>CHPG2632</t>
+          <t>CHPG2634</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,168</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>21,000,000</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>CHPG2633</t>
+          <t>CHPG2635</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>24,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>CHPG2634</t>
+          <t>CHPG2636</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>1,168</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>21,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>CHPG2635</t>
+          <t>CHPG2637</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4230,29 +4230,29 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>CHPG2636</t>
+          <t>CHPG2638</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4272,29 +4272,29 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>19,000,000</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>CHPG2637</t>
+          <t>CHPG2639</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>3,800</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4329,14 +4329,14 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>CHPG2638</t>
+          <t>CHPG2640</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>3,100</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>19,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -4371,19 +4371,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>CHPG2639</t>
+          <t>CHPG2641</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4398,34 +4398,34 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>25,600</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>CHPG2640</t>
+          <t>CHPG2642</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -4435,44 +4435,44 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>3,100</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>21/04/2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>CHPG2641</t>
+          <t>CHPG2643</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4482,64 +4482,64 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>25,600</t>
+          <t>24,000</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>CHPG2642</t>
+          <t>CHPG2644</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>24,000</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21/04/2027</t>
+          <t>03/08/2027</t>
         </is>
       </c>
     </row>
@@ -6478,143 +6478,143 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>CMWG2525</t>
+          <t>CMSN2632</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>17 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>03/03/2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>CMWG2527</t>
+          <t>CMSN2633</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>02/09/2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>CMWG2603</t>
+          <t>CMWG2525</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>17 tháng</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>5,600</t>
+          <t>4,500</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>88,000</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>CMWG2610</t>
+          <t>CMWG2527</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6624,49 +6624,49 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>CMWG2611</t>
+          <t>CMWG2603</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>5,600</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -6676,29 +6676,29 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>101,000</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>CMWG2612</t>
+          <t>CMWG2610</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6713,155 +6713,155 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>84,200</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>CMWG2616</t>
+          <t>CMWG2611</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>101,000</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>CMWG2617</t>
+          <t>CMWG2612</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>75,500</t>
+          <t>84,200</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>CMWG2618</t>
+          <t>CMWG2616</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>77,000</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>15/02/2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>CMWG2619</t>
+          <t>CMWG2617</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -6871,86 +6871,86 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>72,200</t>
+          <t>75,500</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>CMWG2620</t>
+          <t>CMWG2618</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>3,200</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>74,000</t>
+          <t>77,000</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>CMWG2621</t>
+          <t>CMWG2619</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6960,34 +6960,34 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>88,000</t>
+          <t>72,200</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>28/12/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>CMWG2622</t>
+          <t>CMWG2620</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -6997,22 +6997,22 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>9.85 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>73,456</t>
+          <t>74,000</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -7024,217 +7024,217 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>CMWG2623</t>
+          <t>CMWG2621</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>9.85 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>82,712</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>CMWG2624</t>
+          <t>CMWG2622</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>9.85 : 1</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>21,500,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>73,456</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>CMWG2625</t>
+          <t>CMWG2623</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>9.85 : 1</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>24,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>82,000</t>
+          <t>82,712</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>CMWG2626</t>
+          <t>CMWG2624</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>21,500,000</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>CMWG2627</t>
+          <t>CMWG2625</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>6,400</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>24,000,000</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>CMWG2628</t>
+          <t>CMWG2626</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -7254,76 +7254,76 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>5,700</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>76,000</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>CMWG2629</t>
+          <t>CMWG2627</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>88,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>CMWG2630</t>
+          <t>CMWG2628</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -7333,49 +7333,49 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>8.88 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>5,700</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>21/04/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>CSHB2606</t>
+          <t>CMWG2629</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7385,39 +7385,39 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>CSHB2607</t>
+          <t>CMWG2630</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>8.88 : 1</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -7427,34 +7427,34 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>15,500</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>21/04/2027</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>CSHB2608</t>
+          <t>CSHB2606</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7469,108 +7469,108 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>CSHB2609</t>
+          <t>CSHB2607</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>16,333</t>
+          <t>15,500</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>CSHB2610</t>
+          <t>CSHB2608</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>15,999</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>CSHB2612</t>
+          <t>CSHB2609</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -7600,29 +7600,29 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>16,789</t>
+          <t>16,333</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>CSHB2613</t>
+          <t>CSHB2612</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7637,24 +7637,24 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>13,100</t>
+          <t>16,789</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>CSHB2614</t>
+          <t>CSHB2613</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7684,66 +7684,66 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>13,100</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>28/12/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>CSHB2615</t>
+          <t>CSHB2614</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>CSHB2616</t>
+          <t>CSHB2615</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -7780,7 +7780,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>CSHB2617</t>
+          <t>CSHB2616</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -7810,24 +7810,24 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>15,500</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>31/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>CSHB2618</t>
+          <t>CSHB2617</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -7842,29 +7842,29 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>15,500</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>31/03/2027</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>CSHB2619</t>
+          <t>CSHB2618</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -7884,39 +7884,39 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>1,068</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>CSHB2620</t>
+          <t>CSHB2619</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7926,118 +7926,118 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,068</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>CSHB2621</t>
+          <t>CSHB2620</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>13,700</t>
+          <t>12,500</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>CSSB2603</t>
+          <t>CSHB2621</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>13,700</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>06/05/2027</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>CSSB2604</t>
+          <t>CSHB2622</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8047,54 +8047,54 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>17,777</t>
+          <t>12,500</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>21/04/2027</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>CSSB2605</t>
+          <t>CSSB2603</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -8104,19 +8104,19 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>17,111</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>06/05/2027</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>CSSB2607</t>
+          <t>CSSB2604</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -8146,150 +8146,150 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>16,888</t>
+          <t>17,777</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>CSTB2533</t>
+          <t>CSSB2605</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>17 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>17,111</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>CSTB2537</t>
+          <t>CSTB2533</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>17 tháng</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>04/03/2027</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>CSTB2603</t>
+          <t>CSTB2537</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>CSTB2606</t>
+          <t>CSTB2603</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán Kỹ Thương ( TCX )</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8299,133 +8299,133 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>CSTB2608</t>
+          <t>CSTB2606</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>CSTB2609</t>
+          <t>CSTB2608</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>CSTB2610</t>
+          <t>CSTB2609</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -8435,24 +8435,24 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>74,700</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>25/03/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>CSTB2611</t>
+          <t>CSTB2610</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8482,61 +8482,61 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>74,700</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>25/12/2026</t>
+          <t>25/03/2027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>CSTB2612</t>
+          <t>CSTB2611</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán Maybank ( MSVN )</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>80,888</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>25/12/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>CSTB2614</t>
+          <t>CSTB2612</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>78,888</t>
+          <t>80,888</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
@@ -11560,91 +11560,91 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>CVIC2606</t>
+          <t>CVIC2607</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán MB ( MBS )</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>12 : 1</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>3,700</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>246,789</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CVIC2607</t>
+          <t>CVIC2608</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán MB ( MBS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>12 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>221,200</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>CVIC2608</t>
+          <t>CVIC2609</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -11664,17 +11664,17 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>221,200</t>
+          <t>244,000</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -11686,49 +11686,49 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CVIC2609</t>
+          <t>CVIC2610</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>CVIC2610</t>
+          <t>CVIC2611</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -11753,34 +11753,34 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CVIC2611</t>
+          <t>CVIC2612</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -11790,29 +11790,29 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>6,200</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>248,000</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>CVIC2612</t>
+          <t>CVIC2613</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>6,200</t>
+          <t>8,400</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -11842,19 +11842,19 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>248,000</t>
+          <t>224,000</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CVIC2613</t>
+          <t>CVIC2614</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11874,34 +11874,34 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>8,300</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>224,000</t>
+          <t>248,000</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>CVIC2614</t>
+          <t>CVJC2603</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11911,34 +11911,34 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>15.38 : 1</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>8,300</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>248,000</t>
+          <t>158,205</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CVJC2602</t>
+          <t>CVJC2604</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11963,44 +11963,44 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>152,252</t>
+          <t>154,606</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>CVJC2603</t>
+          <t>CVJC2605</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
@@ -12010,39 +12010,39 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>158,205</t>
+          <t>132,500</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CVJC2604</t>
+          <t>CVJC2606</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>15.38 : 1</t>
+          <t>20 : 1</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -12052,66 +12052,66 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>154,606</t>
+          <t>153,500</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>CVJC2605</t>
+          <t>CVNM2523</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>14 tháng</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>9.56 : 1</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>132,500</t>
+          <t>60,322</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>04/12/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CVJC2606</t>
+          <t>CVNM2601</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -12121,175 +12121,175 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>20 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>153,500</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>CVNM2523</t>
+          <t>CVNM2603</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>14 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>9.56 : 1</t>
+          <t>8 : 1</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>60,322</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>06/01/2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CVNM2601</t>
+          <t>CVNM2605</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>CVNM2603</t>
+          <t>CVNM2606</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>11 tháng</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>8 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>06/01/2027</t>
+          <t>06/04/2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CVNM2605</t>
+          <t>CVNM2607</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -12299,71 +12299,71 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>CVNM2606</t>
+          <t>CVNM2609</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Phú Hưng ( PHS )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>11 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>70,111</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>06/04/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CVNM2607</t>
+          <t>CVNM2613</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12373,170 +12373,170 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>2.91 : 1</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>CVNM2609</t>
+          <t>CVNM2614</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>3.88 : 1</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>70,111</t>
+          <t>56,209</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>12/03/2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CVNM2613</t>
+          <t>CVNM2615</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>2.91 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>54,500</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>27/04/2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>CVNM2614</t>
+          <t>CVNM2616</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Thành phố Hồ Chí Minh ( HCM )</t>
+          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>3.88 : 1</t>
+          <t>10 : 1</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>56,209</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CVNM2615</t>
+          <t>CVNM2617</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán VNDIRECT ( VND )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -12546,197 +12546,197 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>2,068</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>54,500</t>
+          <t>58,000</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>27/04/2027</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>CVNM2616</t>
+          <t>CVNM2618</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng Khoán Shinhan Việt Nam ( SSV )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>10 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>68,000</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CVNM2617</t>
+          <t>CVNM2619</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>6 : 1</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>2,068</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>58,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>CVNM2618</t>
+          <t>CVNM2620</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>4 tháng</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>1,468</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>13,000,000</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>68,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>31/12/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CVNM2619</t>
+          <t>CVNM2621</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>6 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>09/02/2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>CVNM2620</t>
+          <t>CVNM2622</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>4,300</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>13,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -12771,61 +12771,61 @@
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>01/04/2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CVNM2621</t>
+          <t>CVNM2623</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>29/03/2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>CVNM2622</t>
+          <t>CVNM2624</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -12835,39 +12835,39 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>7 : 1</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>61,000</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>01/04/2027</t>
+          <t>21/04/2027</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CVNM2623</t>
+          <t>CVNM2625</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán Vietcap ( VCI )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -12877,69 +12877,69 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>70,300</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>29/03/2027</t>
+          <t>03/05/2027</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>CVNM2624</t>
+          <t>CVNM2626</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>7 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>61,000</t>
+          <t>70,300</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>21/04/2027</t>
+          <t>03/08/2027</t>
         </is>
       </c>
     </row>
@@ -13996,195 +13996,195 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>CVRE2526</t>
+          <t>CVPB2631</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>15 tháng</t>
+          <t>5 tháng</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>4 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>27,900</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>03/03/2027</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CVRE2603</t>
+          <t>CVPB2632</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán Pinetree ( Pinetree )</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>10 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>27,900</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>03/06/2027</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>CVRE2604</t>
+          <t>CVRE2526</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>7 tháng</t>
+          <t>15 tháng</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>2,300</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>35,999</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>14/01/2027</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CVRE2605</t>
+          <t>CVRE2603</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>10 tháng</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>37,456</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>CVRE2606</t>
+          <t>CVRE2604</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>7 tháng</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
@@ -14194,155 +14194,155 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>28,103</t>
+          <t>35,999</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>24/12/2026</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CVRE2607</t>
+          <t>CVRE2605</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAI )</t>
+          <t>CTCP Chứng khoán KIS Việt Nam ( KIS )</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>12 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>3.86 : 1</t>
+          <t>5 : 1</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>1,100</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>31,870</t>
+          <t>37,456</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>28/06/2027</t>
+          <t>26/11/2026</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>CVRE2608</t>
+          <t>CVRE2606</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>9 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>28,103</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>12/05/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CVRE2609</t>
+          <t>CVRE2607</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPS ( LPS )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>6 tháng</t>
+          <t>12 tháng</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3.86 : 1</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>31,870</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>11/02/2027</t>
+          <t>28/06/2027</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>CVRE2610</t>
+          <t>CVRE2608</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>8 tháng</t>
+          <t>9 tháng</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -14352,39 +14352,39 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,268</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>22/04/2027</t>
+          <t>12/05/2027</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CVRE2611</t>
+          <t>CVRE2609</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>4 tháng</t>
+          <t>6 tháng</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
@@ -14394,54 +14394,54 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>2,468</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>11/02/2027</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>CVRE2612</t>
+          <t>CVRE2610</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán SSI ( SSI )</t>
+          <t>Công ty TNHH Chứng khoán ACB ( ACBS )</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>5 tháng</t>
+          <t>8 tháng</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>4,600</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
@@ -14451,47 +14451,131 @@
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>09/02/2027</t>
+          <t>22/04/2027</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
+          <t>CVRE2611</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>4 tháng</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>8,000,000</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>CVRE2612</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>CTCP Chứng khoán SSI ( SSI )</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>5 tháng</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>8,000,000</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>09/02/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
           <t>CVRE2613</t>
         </is>
       </c>
-      <c r="B334" s="2" t="inlineStr">
+      <c r="B336" s="2" t="inlineStr">
         <is>
           <t>CTCP Chứng khoán SSI ( SSI )</t>
         </is>
       </c>
-      <c r="C334" s="2" t="inlineStr">
+      <c r="C336" s="2" t="inlineStr">
         <is>
           <t>7 tháng</t>
         </is>
       </c>
-      <c r="D334" s="2" t="inlineStr">
+      <c r="D336" s="2" t="inlineStr">
         <is>
           <t>2 : 1</t>
         </is>
       </c>
-      <c r="E334" s="2" t="inlineStr">
+      <c r="E336" s="2" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="F334" s="2" t="inlineStr">
+      <c r="F336" s="2" t="inlineStr">
         <is>
           <t>7,000,000</t>
         </is>
       </c>
-      <c r="G334" s="2" t="inlineStr">
+      <c r="G336" s="2" t="inlineStr">
         <is>
           <t>27,000</t>
         </is>
       </c>
-      <c r="H334" s="2" t="inlineStr">
+      <c r="H336" s="2" t="inlineStr">
         <is>
           <t>01/04/2027</t>
         </is>

--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -5705,7 +5705,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
